--- a/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-bodystructure.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-bodystructure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-31</t>
+    <t>2024-11-18</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-bodystructure.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-bodystructure.xlsx
@@ -266,7 +266,7 @@
 </t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
@@ -347,7 +347,7 @@
     <t>拡張値の値 - データ型の制約付きセットの1つでなければなりません（リストの[拡張性]（拡張性]（拡張性。html）を参照）。 / Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-bodystructure.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-bodystructure.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-dev</t>
+    <t>1.3.0-dev</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-18</t>
+    <t>2024-12-30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-bodystructure.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-bodystructure.xlsx
@@ -737,17 +737,17 @@
   <dimension ref="A1:AK10"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="27.703125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="27.703125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="12.64453125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="23.75" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="23.75" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="10.83984375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="17.24609375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="14.78515625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -756,23 +756,23 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="21.57421875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="56.546875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="23.95703125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="48.48046875" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="20.5390625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="46.53125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="39.890625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
